--- a/database.xlsx
+++ b/database.xlsx
@@ -871,7 +871,7 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>[{"id":"c-1","startDate":"2019-04-01","affiliation":"Orbit","role":"代表","description":"創業"}]</t>
+          <t>[{"id":"c-1","startDate":"2019-04-01","affiliation":"Ohsumi","role":"代表","description":"創業"}]</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
